--- a/etf_holdings/2026-10-08_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.33%341,000</t>
+          <t>8.43%341,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>8.43%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.39%518,000</t>
+          <t>6.45%518,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4835</v>
+        <v>6000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.93%128,000</t>
+          <t>6.02%106,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>6.02%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>128000</v>
+        <v>106000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.73%165,000</t>
+          <t>5.96%176,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>165000</v>
+        <v>176000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5950</v>
+        <v>1075</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.53%98,000</t>
+          <t>4.68%446,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>4.68%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>98000</v>
+        <v>446000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8460</v>
+        <v>17485</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.05%64,000</t>
+          <t>4.34%25,600</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.05%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>64000</v>
+        <v>25600</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1100</v>
+        <v>5575</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.32%429,000</t>
+          <t>4.17%79,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>429000</v>
+        <v>79000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5530</v>
+        <v>2240</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.27%80,000</t>
+          <t>4.17%195,191</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80000</v>
+        <v>195191</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2240</v>
+        <v>1740</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.12%191,191</t>
+          <t>4.01%244,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>191191</v>
+        <v>244000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.52%248,000</t>
+          <t>3.96%280,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>248000</v>
+        <v>280000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17750</v>
+        <v>8360</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.50%19,600</t>
+          <t>3.63%45,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>19600</v>
+        <v>45000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.03%612,000</t>
+          <t>2.98%607,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>612000</v>
+        <v>607000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>148.5</v>
+        <v>310</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.63%1,893,000</t>
+          <t>2.36%786,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1893000</v>
+        <v>786000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6805</v>
+        <v>592</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.60%39,000</t>
+          <t>2.24%395,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>39000</v>
+        <v>395000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:29</t>
+          <t>2026-10-08 23:49:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1720</v>
+        <v>10615</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.56%155,000</t>
+          <t>2.14%19,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>155000</v>
+        <v>19000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2015</v>
+        <v>147.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.43%126,000</t>
+          <t>1.91%1,345,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>126000</v>
+        <v>1345000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11790</v>
+        <v>744</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.34%19,000</t>
+          <t>1.68%240,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>19000</v>
+        <v>240000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>647</v>
+        <v>1525</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.23%378,000</t>
+          <t>1.67%114,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>378000</v>
+        <v>114000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-0.98%1010</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1990</v>
+        <v>1010</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.03%105,000</t>
+          <t>1.65%169,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>105000</v>
+        <v>169000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.13%179.5</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>179.5</v>
+        <v>6660</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.98%1,187,000</t>
+          <t>1.63%25,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1187000</v>
+        <v>25000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.41%559</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>559</v>
+        <v>4690</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.84%344,000</t>
+          <t>1.57%34,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>344000</v>
+        <v>34000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>-1.39%177</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2315</v>
+        <v>177</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.75%80,000</t>
+          <t>1.54%896,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>80000</v>
+        <v>896000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-0.82%727</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6845</v>
+        <v>727</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.61%25,000</t>
+          <t>1.39%199,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>25000</v>
+        <v>199000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>314</v>
+        <v>2960</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.49%541,000</t>
+          <t>1.23%41,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>541000</v>
+        <v>41000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>595</v>
+        <v>2070</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.30%240,000</t>
+          <t>1.14%59,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>240000</v>
+        <v>59000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,30 +2029,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-2.3%1060</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1020</v>
+        <v>1060</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.05%108,000</t>
+          <t>1.12%108,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.14%796</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>796</v>
+        <v>2370</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.76%102,000</t>
+          <t>1.10%47,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>102000</v>
+        <v>47000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>-1.19%581</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>732</v>
+        <v>581</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.61%87,000</t>
+          <t>1.07%191,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>87000</v>
+        <v>191000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.68%733</t>
+          <t>+3.27%110.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>733</v>
+        <v>110.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.60%87,000</t>
+          <t>1.05%1,023,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>87000</v>
+        <v>1023000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:30</t>
+          <t>2026-10-08 23:49:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3324雙鴻</t>
+          <t>6257矽格</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.33%1525</t>
+          <t>+1.8%283</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1525</v>
+        <v>283</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.58%40,000</t>
+          <t>0.98%368,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>40000</v>
+        <v>368000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2006東和鋼鐵</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.81%85.9</t>
+          <t>-1.17%1685</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>85.90000000000001</v>
+        <v>1685</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.56%681,000</t>
+          <t>0.94%58,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>681000</v>
+        <v>58000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3140</v>
+        <v>557</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.50%18,000</t>
+          <t>0.91%172,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>18000</v>
+        <v>172000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%145.5</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>145.5</v>
+        <v>7165</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.48%348,000</t>
+          <t>0.84%13,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>348000</v>
+        <v>13000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-0.18%558</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2455</v>
+        <v>558</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.48%21,000</t>
+          <t>0.82%154,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>21000</v>
+        <v>154000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.04%96.8</t>
+          <t>0%582</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>96.8</v>
+        <v>582</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.42%463,000</t>
+          <t>0.72%130,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>463000</v>
+        <v>130000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.42%107</t>
+          <t>-0.83%297.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>107</v>
+        <v>297.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.35%368,000</t>
+          <t>0.61%214,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>368000</v>
+        <v>214000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2606裕民</t>
+          <t>3042晶技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.06%74.5</t>
+          <t>+0.24%211</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>74.5</v>
+        <v>211</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.34%486,000</t>
+          <t>0.55%274,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>486000</v>
+        <v>274000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3532台勝科</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+9.85%513</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>513</v>
+        <v>2330</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.34%78,000</t>
+          <t>0.50%22,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>78000</v>
+        <v>22000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-2.99%552</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2400</v>
+        <v>552</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.31%14,000</t>
+          <t>0.48%89,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>14000</v>
+        <v>89000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3406玉晶光</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3.83%1085</t>
+          <t>-1.88%1305</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3.83%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1085</v>
+        <v>1305</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.31%32,000</t>
+          <t>0.47%37,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>32000</v>
+        <v>37000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.69%232.5</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>232.5</v>
+        <v>256</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.29%131,000</t>
+          <t>0.47%198,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>131000</v>
+        <v>198000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.52%582</t>
+          <t>+0.81%248</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>582</v>
+        <v>248</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.28%52,000</t>
+          <t>0.43%184,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>52000</v>
+        <v>184000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>+1.05%48.25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>246</v>
+        <v>48.25</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.25%107,000</t>
+          <t>0.37%810,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>107000</v>
+        <v>810000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,34 +3127,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2606裕民</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.44%106</t>
+          <t>+0.54%74.9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>106</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.25%259,000</t>
+          <t>0.37%526,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>259000</v>
+        <v>526000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:32</t>
+          <t>2026-10-08 23:49:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,407 +3188,41 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.33%300</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>300</v>
+        <v>2360</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.24%86,000</t>
+          <t>0.31%14,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>86000</v>
+        <v>14000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>6147頎邦</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>+6.93%231.5</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>+6.93%</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>0.22%110,000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2027大成鋼</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>+0.1%47.75</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>+0.1%</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>0.20%447,000</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>447000</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2618長榮航</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>+0.96%41.95</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>+0.96%</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>41.95</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>0.19%475,000</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>475000</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>8299群聯</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-1.44%2060</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-1.44%</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>2060</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>0.18%9,000</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>9000</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3491昇達科</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-0.58%1705</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-0.58%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>1705</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0.16%10,000</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:28:33</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>5289宜鼎</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-0.4%1260</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1260</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0.02%1,873</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>1873</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-08_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:03</t>
+          <t>2026-10-08 23:54:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:04</t>
+          <t>2026-10-08 23:54:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:06</t>
+          <t>2026-10-08 23:54:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
